--- a/data/valuebets_database_2025-08-08.xlsx
+++ b/data/valuebets_database_2025-08-08.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,10 +505,8 @@
           <t>08/08 10:30</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F2" t="n">
+        <v>60</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,7 +519,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45877.08393209427</v>
+        <v>45877.08393209491</v>
       </c>
     </row>
     <row r="3">
@@ -550,10 +548,8 @@
           <t>17/08 17:00</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F3" t="n">
+        <v>55</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -566,7 +562,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45877.08393209427</v>
+        <v>45877.08393209491</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +591,8 @@
           <t>18/08 00:00</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F4" t="n">
+        <v>60</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -611,7 +605,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45877.08393209427</v>
+        <v>45877.08393209491</v>
       </c>
     </row>
     <row r="5">
@@ -640,10 +634,8 @@
           <t>10/08 13:30</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F5" t="n">
+        <v>50</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -656,7 +648,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45877.08393209427</v>
+        <v>45877.08393209491</v>
       </c>
     </row>
     <row r="6">
@@ -685,10 +677,8 @@
           <t>16/08 17:15</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F6" t="n">
+        <v>55</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -701,7 +691,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45877.08393209427</v>
+        <v>45877.08393209491</v>
       </c>
     </row>
     <row r="7">
@@ -730,10 +720,8 @@
           <t>16/08 21:30</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F7" t="n">
+        <v>60</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -746,7 +734,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45877.08393209427</v>
+        <v>45877.08393209491</v>
       </c>
     </row>
     <row r="8">
@@ -775,10 +763,8 @@
           <t>13/08 00:30</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F8" t="n">
+        <v>60</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -791,7 +777,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45877.08393209427</v>
+        <v>45877.08393209491</v>
       </c>
     </row>
     <row r="9">
@@ -820,10 +806,8 @@
           <t>17/08 17:00</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F9" t="n">
+        <v>50</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -836,7 +820,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45877.08393209427</v>
+        <v>45877.08393209491</v>
       </c>
     </row>
     <row r="10">
@@ -865,10 +849,8 @@
           <t>09/08 00:15</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F10" t="n">
+        <v>50</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -881,7 +863,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45877.08393209427</v>
+        <v>45877.08393209491</v>
       </c>
     </row>
     <row r="11">
@@ -910,10 +892,8 @@
           <t>16/08 00:00</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F11" t="n">
+        <v>45</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,7 +906,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45877.08393209427</v>
+        <v>45877.08393209491</v>
       </c>
     </row>
     <row r="12">
@@ -955,10 +935,8 @@
           <t>08/08 15:00</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F12" t="n">
+        <v>50</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -971,7 +949,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45877.08393209427</v>
+        <v>45877.08393209491</v>
       </c>
     </row>
     <row r="13">
@@ -1000,10 +978,8 @@
           <t>09/08 18:00</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F13" t="n">
+        <v>55</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1016,7 +992,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45877.08393209427</v>
+        <v>45877.08393209491</v>
       </c>
     </row>
     <row r="14">
@@ -1045,10 +1021,8 @@
           <t>12/08 18:15</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F14" t="n">
+        <v>60</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1061,7 +1035,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45877.08393209427</v>
+        <v>45877.08393209491</v>
       </c>
     </row>
     <row r="15">
@@ -1090,10 +1064,8 @@
           <t>16/08 19:15</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F15" t="n">
+        <v>45</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1106,7 +1078,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45877.08393209427</v>
+        <v>45877.08393209491</v>
       </c>
     </row>
     <row r="16">
@@ -1135,10 +1107,8 @@
           <t>08/08 22:00</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F16" t="n">
+        <v>50</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1151,7 +1121,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45877.08393209427</v>
+        <v>45877.08393209491</v>
       </c>
     </row>
     <row r="17">
@@ -1180,10 +1150,8 @@
           <t>09/08 20:00</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F17" t="n">
+        <v>55</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1196,7 +1164,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45877.08393209427</v>
+        <v>45877.08393209491</v>
       </c>
     </row>
     <row r="18">
@@ -1225,10 +1193,8 @@
           <t>15/08 17:30</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F18" t="n">
+        <v>50</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1241,7 +1207,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45877.08393209427</v>
+        <v>45877.08393209491</v>
       </c>
     </row>
     <row r="19">
@@ -1270,10 +1236,8 @@
           <t>10/08 23:30</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F19" t="n">
+        <v>55</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1286,7 +1250,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45877.08393209427</v>
+        <v>45877.08393209491</v>
       </c>
     </row>
     <row r="20">
@@ -1315,10 +1279,8 @@
           <t>09/08 16:00</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F20" t="n">
+        <v>60</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1331,7 +1293,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45877.08393209427</v>
+        <v>45877.08393209491</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1322,8 @@
           <t>09/08 18:00</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F21" t="n">
+        <v>55</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1376,7 +1336,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45877.08393209427</v>
+        <v>45877.08393209491</v>
       </c>
     </row>
     <row r="22">
@@ -1405,10 +1365,8 @@
           <t>10/08 00:00</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F22" t="n">
+        <v>60</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1421,7 +1379,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45877.08393209427</v>
+        <v>45877.08393209491</v>
       </c>
     </row>
     <row r="23">
@@ -1450,10 +1408,8 @@
           <t>09/08 12:30</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F23" t="n">
+        <v>45</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1466,7 +1422,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45877.08393209427</v>
+        <v>45877.08393209491</v>
       </c>
     </row>
     <row r="24">
@@ -1495,10 +1451,8 @@
           <t>08/08 18:45</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F24" t="n">
+        <v>45</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1511,7 +1465,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45877.08393209427</v>
+        <v>45877.08393209491</v>
       </c>
     </row>
     <row r="25">
@@ -1540,10 +1494,8 @@
           <t>12/08 18:00</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F25" t="n">
+        <v>55</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1556,7 +1508,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45877.08393209427</v>
+        <v>45877.08393209491</v>
       </c>
     </row>
     <row r="26">
@@ -1585,23 +1537,111 @@
           <t>08/08 18:30</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" t="n">
+        <v>50</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2,20%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>+10,3%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>45877.08393209491</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Barracas C</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Barracas Central – CA AldosiviLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>10/08 18:00</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2,86%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+57,1%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45877.15883087553</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Sanfrecce </t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Sanfrecce Hiroshima – Shimizu S-P.J-League</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>10/08 09:30</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>50.00</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>2,20%</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>+10,3%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>45877.08393209427</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+9,48%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45877.15883087553</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-08.xlsx
+++ b/data/valuebets_database_2025-08-08.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1580,10 +1580,8 @@
           <t>10/08 18:00</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F27" t="n">
+        <v>55</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1596,7 +1594,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45877.15883087553</v>
+        <v>45877.15883087963</v>
       </c>
     </row>
     <row r="28">
@@ -1625,23 +1623,111 @@
           <t>10/08 09:30</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" t="n">
+        <v>50</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+9,48%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45877.15883087963</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | FC Slovan </t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>FC Slovan Liberec – FK Dukla PragueSynot League</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>09/08 15:00</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2,46%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+10,5%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45877.20105840956</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Las Palmas</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Las Palmas – FC AndorraLaLiga2</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>17/08 19:30</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>50.00</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>2,19%</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>+9,48%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="n">
-        <v>45877.15883087553</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2,16%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+8,19%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45877.20105840956</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-08.xlsx
+++ b/data/valuebets_database_2025-08-08.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1666,10 +1666,8 @@
           <t>09/08 15:00</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F29" t="n">
+        <v>45</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1682,7 +1680,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45877.20105840956</v>
+        <v>45877.20105841435</v>
       </c>
     </row>
     <row r="30">
@@ -1711,10 +1709,8 @@
           <t>17/08 19:30</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F30" t="n">
+        <v>50</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1727,7 +1723,142 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>45877.20105840956</v>
+        <v>45877.20105841435</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 15.5 - tirs1re équipe | Heerenveen</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Heerenveen – VolendamPays-Bas - Pays-Bas Eredivisie</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Moins que 15.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>09/08 18:00</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>52,2%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+56,5%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45877.23002914377</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 27.5 - tirs | PSV Eindho</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven – Sparta RotterdamPays-Bas - Pays-Bas Eredivisie</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Moins que 27.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>09/08 19:00</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>42,0%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+13,5%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45877.23002914377</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Moins que 6.5 - tirs2e équipe | Feyenoord </t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Feyenoord – NAC BredaPays-Bas - Pays-Bas Eredivisie</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Moins que 6.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>09/08 16:45</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>42,6%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+6,56%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45877.23002914377</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-08.xlsx
+++ b/data/valuebets_database_2025-08-08.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1752,10 +1752,8 @@
           <t>09/08 18:00</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="F31" t="n">
+        <v>3</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1768,7 +1766,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45877.23002914377</v>
+        <v>45877.23002914352</v>
       </c>
     </row>
     <row r="32">
@@ -1797,10 +1795,8 @@
           <t>09/08 19:00</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="F32" t="n">
+        <v>2.7</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1813,7 +1809,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45877.23002914377</v>
+        <v>45877.23002914352</v>
       </c>
     </row>
     <row r="33">
@@ -1842,10 +1838,8 @@
           <t>09/08 16:45</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
+      <c r="F33" t="n">
+        <v>2.5</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1858,7 +1852,97 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45877.23002914377</v>
+        <v>45877.23002914352</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Moins que 15.5 - tirs2e équipe | Gazisehir </t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Gazisehir Gaziantep FK – GalatasarayTurquie - Turquie Super Lig</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Moins que 15.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>08/08 18:30</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>42,5%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+14,7%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45877.27629331114</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 3.5 - tir cadré2e équipe | Korona Kie</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Korona Kielce – RKS RadomiakPologne - Pologne Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Moins que 3.5 - tir cadré2e équipe</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>08/08 16:00</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>39,3%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+8,18%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45877.27629331114</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-08.xlsx
+++ b/data/valuebets_database_2025-08-08.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1881,10 +1881,8 @@
           <t>08/08 18:30</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="F34" t="n">
+        <v>2.7</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1897,7 +1895,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45877.27629331114</v>
+        <v>45877.27629331018</v>
       </c>
     </row>
     <row r="35">
@@ -1926,23 +1924,291 @@
           <t>08/08 16:00</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F35" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>39,3%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+8,18%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45877.27629331018</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 9.5 - tirs1re équipe | Crystal Pa</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Crystal Palace – LiverpoolAngleterre - A. Community Shield</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Moins que 9.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>10/08 14:00</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>45,4%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+27,1%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45877.31108529995</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 26.5 - tirs | Bahia Salv</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Bahia Salvador BA – FluminenseBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Plus que 26.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>10/08 00:00</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>36,3%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+19,9%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45877.31108529995</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 16.5 - tirs1re équipe | Flamengo –</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Flamengo – MirassolBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Moins que 16.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>09/08 21:30</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>41,6%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+12,4%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45877.31108529995</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 11.5 - tir cadré | Philadelph</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Philadelphia Union – Toronto FCÉtats-Unis - États-Unis MLS</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Plus que 11.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>09/08 23:30</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>30,5%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+9,88%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45877.31108529995</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | H 2 (−1.5) | Jannik Sin</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Jannik Sinner – Daniel Elahi GalanATP 1000 Cincinnati</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>H 2 (−1.5)</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>09/08 15:00</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1,98%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+9,10%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45877.31108529995</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 13.5 - tirs1re équipe | Sint-Truid</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Sint-Truidense VV – FCV Dender EHBelgique - Belgique Division 1A</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Moins que 13.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>08/08 18:45</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
         <is>
           <t>2.75</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>39,3%</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>+8,18%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="n">
-        <v>45877.27629331114</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>39,6%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+8,90%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45877.31108529995</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-08.xlsx
+++ b/data/valuebets_database_2025-08-08.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1967,10 +1967,8 @@
           <t>10/08 14:00</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
+      <c r="F36" t="n">
+        <v>2.8</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1983,7 +1981,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45877.31108529995</v>
+        <v>45877.31108530093</v>
       </c>
     </row>
     <row r="37">
@@ -2012,10 +2010,8 @@
           <t>10/08 00:00</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
+      <c r="F37" t="n">
+        <v>3.3</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2028,7 +2024,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45877.31108529995</v>
+        <v>45877.31108530093</v>
       </c>
     </row>
     <row r="38">
@@ -2057,10 +2053,8 @@
           <t>09/08 21:30</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="F38" t="n">
+        <v>2.7</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2073,7 +2067,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>45877.31108529995</v>
+        <v>45877.31108530093</v>
       </c>
     </row>
     <row r="39">
@@ -2102,10 +2096,8 @@
           <t>09/08 23:30</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
+      <c r="F39" t="n">
+        <v>3.6</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2118,7 +2110,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>45877.31108529995</v>
+        <v>45877.31108530093</v>
       </c>
     </row>
     <row r="40">
@@ -2147,10 +2139,8 @@
           <t>09/08 15:00</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F40" t="n">
+        <v>55</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2163,7 +2153,7 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>45877.31108529995</v>
+        <v>45877.31108530093</v>
       </c>
     </row>
     <row r="41">
@@ -2192,10 +2182,8 @@
           <t>08/08 18:45</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
+      <c r="F41" t="n">
+        <v>2.75</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2208,7 +2196,367 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45877.31108529995</v>
+        <v>45877.31108530093</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 25.5 - tirs | Heerenveen</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Heerenveen – VolendamPays-Bas - Pays-Bas Eredivisie</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Moins que 25.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>09/08 18:00</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2.95</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>46,9%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>+38,3%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>45877.3562855175</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 2.52e équipe | Dinamo Zag</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Dinamo Zagreb – HNK Vukovar 1991HNL</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Plus que 2.52e équipe</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>08/08 19:00</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+21,1%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45877.3562855175</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 29.5 - tirs | Bragantino</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Bragantino – Internacional RSBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Plus que 29.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>09/08 21:30</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>35,3%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+16,5%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45877.3562855175</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Jeonbuk Mo</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Jeonbuk Motors – FC AnyangK League 1</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>08/08 10:30</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2,65%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+6,02%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45877.3562855175</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Plus que 21.5 - tirs1re équipe | Feyenoord </t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Feyenoord – NAC BredaPays-Bas - Pays-Bas Eredivisie</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Plus que 21.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>09/08 16:45</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>38,8%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+2,77%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45877.3562855175</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Northampto</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Northampton Town – SouthamptonEFL Cup</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>12/08 18:45</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2,05%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+2,54%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45877.3562855175</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Atlético B</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga – Santa FePrimera A</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>10/08 00:30</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2,54%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+1,44%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>45877.3562855175</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Linfield –</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Linfield – Dungannon FCNIFL Premiership</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>10/08 14:00</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>35.00</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2,86%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>+0,03%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>45877.3562855175</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-08.xlsx
+++ b/data/valuebets_database_2025-08-08.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2225,10 +2225,8 @@
           <t>09/08 18:00</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2.95</t>
-        </is>
+      <c r="F42" t="n">
+        <v>2.95</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2241,7 +2239,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45877.3562855175</v>
+        <v>45877.35628552084</v>
       </c>
     </row>
     <row r="43">
@@ -2270,10 +2268,8 @@
           <t>08/08 19:00</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F43" t="n">
+        <v>50</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2286,7 +2282,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45877.3562855175</v>
+        <v>45877.35628552084</v>
       </c>
     </row>
     <row r="44">
@@ -2315,10 +2311,8 @@
           <t>09/08 21:30</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
+      <c r="F44" t="n">
+        <v>3.3</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2331,7 +2325,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45877.3562855175</v>
+        <v>45877.35628552084</v>
       </c>
     </row>
     <row r="45">
@@ -2360,10 +2354,8 @@
           <t>08/08 10:30</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F45" t="n">
+        <v>40</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2376,7 +2368,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45877.3562855175</v>
+        <v>45877.35628552084</v>
       </c>
     </row>
     <row r="46">
@@ -2405,10 +2397,8 @@
           <t>09/08 16:45</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2.65</t>
-        </is>
+      <c r="F46" t="n">
+        <v>2.65</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2421,7 +2411,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45877.3562855175</v>
+        <v>45877.35628552084</v>
       </c>
     </row>
     <row r="47">
@@ -2450,10 +2440,8 @@
           <t>12/08 18:45</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F47" t="n">
+        <v>50</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2466,7 +2454,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>45877.3562855175</v>
+        <v>45877.35628552084</v>
       </c>
     </row>
     <row r="48">
@@ -2495,10 +2483,8 @@
           <t>10/08 00:30</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F48" t="n">
+        <v>40</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2511,7 +2497,7 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45877.3562855175</v>
+        <v>45877.35628552084</v>
       </c>
     </row>
     <row r="49">
@@ -2540,10 +2526,8 @@
           <t>10/08 14:00</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>35.00</t>
-        </is>
+      <c r="F49" t="n">
+        <v>35</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2556,7 +2540,232 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>45877.3562855175</v>
+        <v>45877.35628552084</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 5.5 | CA Tigre –</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>CA Tigre – CA HuracanLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Plus que 5.5</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>08/08 22:00</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>80.00</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>1,88%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>+50,3%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>45877.39600216825</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 2 - aces | A.Blinkova</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>A.Blinkova – K.BirrellWTA - Cincinnati F</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>08/08 16:10</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>39,0%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>+36,6%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>45877.39600216825</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 2 - aces | P.Kudermet</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>P.Kudermetova – E.SeidelWTA - Cincinnati F</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>08/08 16:10</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>62,8%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>+16,2%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>45877.39600216825</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 1 - aces | S.Kartal –</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>S.Kartal – C.GarciaWTA - Cincinnati F</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>08/08 15:00</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>29,0%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>+16,1%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>45877.39600216825</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | FC Polissy</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>FC Polissya Zhytomyr – Kolos KovalivkaUPL</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>10/08 12:30</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>+8,26%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>45877.39600216825</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-08.xlsx
+++ b/data/valuebets_database_2025-08-08.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2569,10 +2569,8 @@
           <t>08/08 22:00</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>80.00</t>
-        </is>
+      <c r="F50" t="n">
+        <v>80</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2585,7 +2583,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>45877.39600216825</v>
+        <v>45877.39600216435</v>
       </c>
     </row>
     <row r="51">
@@ -2614,10 +2612,8 @@
           <t>08/08 16:10</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
+      <c r="F51" t="n">
+        <v>3.5</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2630,7 +2626,7 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>45877.39600216825</v>
+        <v>45877.39600216435</v>
       </c>
     </row>
     <row r="52">
@@ -2659,10 +2655,8 @@
           <t>08/08 16:10</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
+      <c r="F52" t="n">
+        <v>1.85</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2675,7 +2669,7 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>45877.39600216825</v>
+        <v>45877.39600216435</v>
       </c>
     </row>
     <row r="53">
@@ -2704,10 +2698,8 @@
           <t>08/08 15:00</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
+      <c r="F53" t="n">
+        <v>4</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2720,7 +2712,7 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>45877.39600216825</v>
+        <v>45877.39600216435</v>
       </c>
     </row>
     <row r="54">
@@ -2749,10 +2741,8 @@
           <t>10/08 12:30</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F54" t="n">
+        <v>50</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2765,7 +2755,52 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45877.39600216825</v>
+        <v>45877.39600216435</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Club Sport</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Club Sportivo Luqueno – CA Tembetary YpanePrimera Division</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>09/08 21:30</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>+8,77%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>45877.43526742719</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-08.xlsx
+++ b/data/valuebets_database_2025-08-08.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2784,10 +2784,8 @@
           <t>09/08 21:30</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F55" t="n">
+        <v>45</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2800,7 +2798,52 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>45877.43526742719</v>
+        <v>45877.43526743056</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Cerro Port</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Cerro Porteno – Nacional AsuncionPrimera Division</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>08/08 21:30</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>+54,6%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>45877.47295304714</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-08.xlsx
+++ b/data/valuebets_database_2025-08-08.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2827,10 +2827,8 @@
           <t>08/08 21:30</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F56" t="n">
+        <v>60</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2843,7 +2841,97 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>45877.47295304714</v>
+        <v>45877.47295304398</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ParionsSport(FR)Volleyball | Moins que 3.5 | Croatie F </t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Volleyball</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Croatie F – Kosovo FMonde - Euro QF</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Moins que 3.5</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>09/08 17:00</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>94,6%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>+27,6%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>45877.53559464043</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Utrecht – </t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Utrecht – Servette FCLigue Europa</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>14/08 18:00</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2,93%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>+17,1%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>45877.53559464043</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-08.xlsx
+++ b/data/valuebets_database_2025-08-08.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2870,10 +2870,8 @@
           <t>09/08 17:00</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
+      <c r="F57" t="n">
+        <v>1.35</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2886,7 +2884,7 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>45877.53559464043</v>
+        <v>45877.5355946412</v>
       </c>
     </row>
     <row r="58">
@@ -2915,23 +2913,291 @@
           <t>14/08 18:00</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F58" t="n">
+        <v>40</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2,93%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>+17,1%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>45877.5355946412</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | CA Tigre –</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>CA Tigre – CA HuracanLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>08/08 22:00</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>+46,6%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>45877.57001997799</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 2 - aces | Anna Blink</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Anna Blinkova – Kimberly BirrellWTA - Cincinnati</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>08/08 17:00</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>39,0%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>+26,8%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>45877.57001997799</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Shakhtar D</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Shakhtar Donetsk – PanathinaikosLigue Europa</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>14/08 18:00</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
         <is>
           <t>40.00</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>2,93%</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>+17,1%</t>
         </is>
       </c>
-      <c r="I58" s="2" t="n">
-        <v>45877.53559464043</v>
+      <c r="I61" s="2" t="n">
+        <v>45877.57001997799</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Winamax(FR)Tennis | 2 - aces | Catherine </t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Catherine McNally – Maddison InglisWTA - Cincinnati</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>09/08 01:00</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>57,9%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>+15,8%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>45877.57001997799</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Beach volley | 21-2 | Bello / Be</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Beach volley</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Bello / Bello – Cottafava / Dal CorsoBaden Challenge H.</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>21-2</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>08/08 14:00</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>35,8%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>+14,6%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>45877.57001997799</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 2 - aces | Danielle C</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Danielle Collins – Taylor TownsendWTA - Cincinnati</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>08/08 17:00</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>81,7%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>+14,3%</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>45877.57001997799</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-08.xlsx
+++ b/data/valuebets_database_2025-08-08.xlsx
@@ -2956,10 +2956,8 @@
           <t>08/08 22:00</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F59" t="n">
+        <v>60</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2972,7 +2970,7 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>45877.57001997799</v>
+        <v>45877.57001997685</v>
       </c>
     </row>
     <row r="60">
@@ -3001,10 +2999,8 @@
           <t>08/08 17:00</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
+      <c r="F60" t="n">
+        <v>3.25</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3017,7 +3013,7 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>45877.57001997799</v>
+        <v>45877.57001997685</v>
       </c>
     </row>
     <row r="61">
@@ -3046,10 +3042,8 @@
           <t>14/08 18:00</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F61" t="n">
+        <v>40</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3062,7 +3056,7 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>45877.57001997799</v>
+        <v>45877.57001997685</v>
       </c>
     </row>
     <row r="62">
@@ -3091,10 +3085,8 @@
           <t>09/08 01:00</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
+      <c r="F62" t="n">
+        <v>2</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3107,7 +3099,7 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>45877.57001997799</v>
+        <v>45877.57001997685</v>
       </c>
     </row>
     <row r="63">
@@ -3136,10 +3128,8 @@
           <t>08/08 14:00</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="F63" t="n">
+        <v>3.2</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3152,7 +3142,7 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>45877.57001997799</v>
+        <v>45877.57001997685</v>
       </c>
     </row>
     <row r="64">
@@ -3181,10 +3171,8 @@
           <t>08/08 17:00</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
+      <c r="F64" t="n">
+        <v>1.4</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3197,7 +3185,7 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>45877.57001997799</v>
+        <v>45877.57001997685</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-08.xlsx
+++ b/data/valuebets_database_2025-08-08.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3188,6 +3188,51 @@
         <v>45877.57001997685</v>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 2 - aces | M.Uchijima</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>M.Uchijima – C.OsorioWTA - Cincinnati F</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>08/08 17:20</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>21,0%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>+25,9%</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>45877.6430524672</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-08-08.xlsx
+++ b/data/valuebets_database_2025-08-08.xlsx
@@ -3214,10 +3214,8 @@
           <t>08/08 17:20</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
+      <c r="F65" t="n">
+        <v>6</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3230,7 +3228,7 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>45877.6430524672</v>
+        <v>45877.64305246528</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-08.xlsx
+++ b/data/valuebets_database_2025-08-08.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3231,6 +3231,51 @@
         <v>45877.64305246528</v>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 2.52e équipe | Sporting B</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Sporting Braga – CFR ClujLigue Europa stq pr cu 385076e7</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Plus que 2.52e équipe</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>14/08 18:30</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2,43%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>+9,45%</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>45877.72144329703</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-08-08.xlsx
+++ b/data/valuebets_database_2025-08-08.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I66"/>
+  <dimension ref="A1:I68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3257,10 +3257,8 @@
           <t>14/08 18:30</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F66" t="n">
+        <v>45</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3273,7 +3271,97 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>45877.72144329703</v>
+        <v>45877.72144329861</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 2 - aces | J.Brooksby</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>J.Brooksby – A.MullerATP - Cincinnati H</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>08/08 19:15</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>33,4%</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>+8,64%</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>45877.77246117479</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Plus que 10.5 - tir cadré | Fortaleza </t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Fortaleza CE – BotafogoBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Plus que 10.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>09/08 23:30</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>28,2%</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>+7,01%</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>45877.77246117479</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-08.xlsx
+++ b/data/valuebets_database_2025-08-08.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I68"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3300,10 +3300,8 @@
           <t>08/08 19:15</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
+      <c r="F67" t="n">
+        <v>3.25</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3316,7 +3314,7 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>45877.77246117479</v>
+        <v>45877.77246118055</v>
       </c>
     </row>
     <row r="68">
@@ -3345,10 +3343,8 @@
           <t>09/08 23:30</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
+      <c r="F68" t="n">
+        <v>3.8</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3361,7 +3357,97 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>45877.77246117479</v>
+        <v>45877.77246118055</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Bwin(FR)Beach volley | 11-2 | Alfieri/Ra</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Bwin(FR)Beach volley</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Alfieri/Ranghieri (ITA) – Budinger/Evans (USA)Monde - Beach Pro Tour - Challenge Baden (H)</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>11-2</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>09/08 09:00</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>34,3%</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>+9,67%</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>45877.80435098472</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 24.5 - tirs | Crystal Pa</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Crystal Palace – LiverpoolAngleterre - A. Community Shield</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Moins que 24.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>10/08 14:00</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2.95</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>35,9%</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>+5,76%</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>45877.80435098472</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-08.xlsx
+++ b/data/valuebets_database_2025-08-08.xlsx
@@ -3386,10 +3386,8 @@
           <t>09/08 09:00</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="F69" t="n">
+        <v>3.2</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3402,7 +3400,7 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>45877.80435098472</v>
+        <v>45877.8043509838</v>
       </c>
     </row>
     <row r="70">
@@ -3431,10 +3429,8 @@
           <t>10/08 14:00</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2.95</t>
-        </is>
+      <c r="F70" t="n">
+        <v>2.95</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3447,7 +3443,7 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>45877.80435098472</v>
+        <v>45877.8043509838</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-08.xlsx
+++ b/data/valuebets_database_2025-08-08.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I70"/>
+  <dimension ref="A1:I71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3446,6 +3446,51 @@
         <v>45877.8043509838</v>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ParionsSport(FR)Tennis | 2 - aces | C.McNally </t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>C.McNally – M.InglisWTA - Cincinnati F</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>09/08 00:10</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>58,5%</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>+40,3%</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>45877.8897893224</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-08-08.xlsx
+++ b/data/valuebets_database_2025-08-08.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I71"/>
+  <dimension ref="A1:I75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3472,10 +3472,8 @@
           <t>09/08 00:10</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
+      <c r="F71" t="n">
+        <v>2.4</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -3488,7 +3486,187 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>45877.8897893224</v>
+        <v>45877.88978931713</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Tennis | 11-21er set | Lamens – V</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Lamens – V KudermetovaWTA Cincinnati 2025</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>11-21er set</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>08/08 22:30</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>16,5%</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>+7,44%</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>45877.9322097058</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 2.52e équipe | Zeljeznica</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Zeljeznicar – FK Rudar PrijedorPremijer Liga</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Plus que 2.52e équipe</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>09/08 19:00</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2,64%</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>+5,65%</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>45877.9322097058</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 5.5 | Valence – </t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Valence – Real SociedadLaLiga</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Plus que 5.5</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>16/08 19:30</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>2,31%</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>+3,89%</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>45877.9322097058</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Moins que 5.51er set2e participant | Pedro Mart</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Pedro Martinez – Tommy PaulATP 1000 Cincinnati</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Moins que 5.51er set2e participant</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>09/08 16:10</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>6.70</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>15,5%</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>+3,76%</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>45877.9322097058</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-08.xlsx
+++ b/data/valuebets_database_2025-08-08.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I75"/>
+  <dimension ref="A1:I76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3515,10 +3515,8 @@
           <t>08/08 22:30</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
+      <c r="F72" t="n">
+        <v>6.5</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3531,7 +3529,7 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>45877.9322097058</v>
+        <v>45877.93220971065</v>
       </c>
     </row>
     <row r="73">
@@ -3560,10 +3558,8 @@
           <t>09/08 19:00</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F73" t="n">
+        <v>40</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3576,7 +3572,7 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>45877.9322097058</v>
+        <v>45877.93220971065</v>
       </c>
     </row>
     <row r="74">
@@ -3605,10 +3601,8 @@
           <t>16/08 19:30</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F74" t="n">
+        <v>45</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3621,7 +3615,7 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>45877.9322097058</v>
+        <v>45877.93220971065</v>
       </c>
     </row>
     <row r="75">
@@ -3650,10 +3644,8 @@
           <t>09/08 16:10</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>6.70</t>
-        </is>
+      <c r="F75" t="n">
+        <v>6.7</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3666,7 +3658,52 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>45877.9322097058</v>
+        <v>45877.93220971065</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 5.5 | San Martin</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>San Martin de San Juan – CA SarmientoLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Plus que 5.5</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>09/08 17:30</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2,12%</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>+5,97%</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>45877.97386127487</v>
       </c>
     </row>
   </sheetData>
